--- a/artfynd/A 41948-2026 artfynd.xlsx
+++ b/artfynd/A 41948-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137381767</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381755</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381784</v>
       </c>
       <c r="B4" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137381785</v>
       </c>
       <c r="B5" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137381787</v>
       </c>
       <c r="B6" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381842</v>
       </c>
       <c r="B7" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137381849</v>
       </c>
       <c r="B8" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137381862</v>
       </c>
       <c r="B9" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137381715</v>
       </c>
       <c r="B10" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137381782</v>
       </c>
       <c r="B11" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137381837</v>
       </c>
       <c r="B12" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137381769</v>
       </c>
       <c r="B13" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137381806</v>
       </c>
       <c r="B14" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137381699</v>
       </c>
       <c r="B15" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137381730</v>
       </c>
       <c r="B16" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137381739</v>
       </c>
       <c r="B17" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137381749</v>
       </c>
       <c r="B18" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137381877</v>
       </c>
       <c r="B19" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>137381682</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137381691</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137381694</v>
       </c>
       <c r="B23" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137381701</v>
       </c>
       <c r="B24" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137381709</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>137381689</v>
       </c>
       <c r="B26" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>137381768</v>
       </c>
       <c r="B27" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137381774</v>
       </c>
       <c r="B28" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>137381800</v>
       </c>
       <c r="B29" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137381723</v>
       </c>
       <c r="B30" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137381771</v>
       </c>
       <c r="B31" t="n">
-        <v>92846</v>
+        <v>92851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137381692</v>
       </c>
       <c r="B32" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137381828</v>
       </c>
       <c r="B33" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137381841</v>
       </c>
       <c r="B34" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>137381887</v>
       </c>
       <c r="B35" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>137381690</v>
       </c>
       <c r="B36" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>137381802</v>
       </c>
       <c r="B37" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>137381807</v>
       </c>
       <c r="B38" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>137381829</v>
       </c>
       <c r="B39" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137381698</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137381700</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137381702</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>137381703</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>137381704</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>137381706</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>137381708</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137381711</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137381718</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137381720</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>137381721</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>137381724</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>137381729</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>137381734</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>137381735</v>
       </c>
       <c r="B55" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>137381736</v>
       </c>
       <c r="B56" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>137381738</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137381740</v>
       </c>
       <c r="B58" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>137381743</v>
       </c>
       <c r="B59" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>137381746</v>
       </c>
       <c r="B60" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137381747</v>
       </c>
       <c r="B61" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>137381750</v>
       </c>
       <c r="B62" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>137381752</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137381754</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>137381757</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>137381759</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>137381760</v>
       </c>
       <c r="B67" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137381761</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>137381764</v>
       </c>
       <c r="B69" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>137381765</v>
       </c>
       <c r="B70" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>137381772</v>
       </c>
       <c r="B71" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>137381773</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>137381775</v>
       </c>
       <c r="B73" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>137381776</v>
       </c>
       <c r="B74" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>137381779</v>
       </c>
       <c r="B75" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137381780</v>
       </c>
       <c r="B76" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137381783</v>
       </c>
       <c r="B77" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137381786</v>
       </c>
       <c r="B78" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137381789</v>
       </c>
       <c r="B79" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>137381790</v>
       </c>
       <c r="B80" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137381791</v>
       </c>
       <c r="B81" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137381793</v>
       </c>
       <c r="B82" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>137381797</v>
       </c>
       <c r="B83" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137381801</v>
       </c>
       <c r="B84" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>137381803</v>
       </c>
       <c r="B85" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>137381810</v>
       </c>
       <c r="B86" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>137381811</v>
       </c>
       <c r="B87" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137381812</v>
       </c>
       <c r="B88" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137381813</v>
       </c>
       <c r="B89" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137381814</v>
       </c>
       <c r="B90" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>137381815</v>
       </c>
       <c r="B91" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>137381816</v>
       </c>
       <c r="B92" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>137381817</v>
       </c>
       <c r="B93" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>137381819</v>
       </c>
       <c r="B94" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137381824</v>
       </c>
       <c r="B95" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>137381831</v>
       </c>
       <c r="B96" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>137381833</v>
       </c>
       <c r="B97" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>137381834</v>
       </c>
       <c r="B98" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137381835</v>
       </c>
       <c r="B99" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137381836</v>
       </c>
       <c r="B100" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137381843</v>
       </c>
       <c r="B101" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137381844</v>
       </c>
       <c r="B102" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>137381845</v>
       </c>
       <c r="B103" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137381847</v>
       </c>
       <c r="B104" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137381848</v>
       </c>
       <c r="B105" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>137381852</v>
       </c>
       <c r="B106" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>137381853</v>
       </c>
       <c r="B107" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>137381854</v>
       </c>
       <c r="B108" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>137381855</v>
       </c>
       <c r="B109" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137381859</v>
       </c>
       <c r="B110" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137381861</v>
       </c>
       <c r="B111" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137381863</v>
       </c>
       <c r="B112" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137381864</v>
       </c>
       <c r="B113" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>137381867</v>
       </c>
       <c r="B114" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>137381868</v>
       </c>
       <c r="B115" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>137381869</v>
       </c>
       <c r="B116" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>137381871</v>
       </c>
       <c r="B117" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>137381874</v>
       </c>
       <c r="B118" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>137381875</v>
       </c>
       <c r="B119" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>137381876</v>
       </c>
       <c r="B120" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>137381878</v>
       </c>
       <c r="B121" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>137381879</v>
       </c>
       <c r="B122" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137381688</v>
       </c>
       <c r="B123" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>137381732</v>
       </c>
       <c r="B124" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>137381733</v>
       </c>
       <c r="B125" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>137381753</v>
       </c>
       <c r="B126" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>137381858</v>
       </c>
       <c r="B127" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>137381686</v>
       </c>
       <c r="B128" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>137381839</v>
       </c>
       <c r="B129" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>137381707</v>
       </c>
       <c r="B130" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>137381808</v>
       </c>
       <c r="B131" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>137381717</v>
       </c>
       <c r="B132" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>137381710</v>
       </c>
       <c r="B134" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>137381778</v>
       </c>
       <c r="B135" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>137381696</v>
       </c>
       <c r="B136" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>137381712</v>
       </c>
       <c r="B137" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>137381714</v>
       </c>
       <c r="B138" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>137381719</v>
       </c>
       <c r="B139" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>137381728</v>
       </c>
       <c r="B140" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>137381745</v>
       </c>
       <c r="B141" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>137381762</v>
       </c>
       <c r="B142" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>137381763</v>
       </c>
       <c r="B143" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>137381766</v>
       </c>
       <c r="B144" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>137381792</v>
       </c>
       <c r="B145" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>137381804</v>
       </c>
       <c r="B146" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>137381846</v>
       </c>
       <c r="B147" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>137381683</v>
       </c>
       <c r="B162" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>137381685</v>
       </c>
       <c r="B163" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>137381697</v>
       </c>
       <c r="B164" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>137381713</v>
       </c>
       <c r="B165" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>137381818</v>
       </c>
       <c r="B166" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>137381695</v>
       </c>
       <c r="B167" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>137381821</v>
       </c>
       <c r="B168" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>137381823</v>
       </c>
       <c r="B169" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>137381693</v>
       </c>
       <c r="B171" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>137381716</v>
       </c>
       <c r="B172" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 41948-2026 artfynd.xlsx
+++ b/artfynd/A 41948-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137381767</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381755</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381784</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137381785</v>
       </c>
       <c r="B5" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137381787</v>
       </c>
       <c r="B6" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381842</v>
       </c>
       <c r="B7" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137381849</v>
       </c>
       <c r="B8" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137381862</v>
       </c>
       <c r="B9" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137381715</v>
       </c>
       <c r="B10" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137381782</v>
       </c>
       <c r="B11" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137381837</v>
       </c>
       <c r="B12" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137381769</v>
       </c>
       <c r="B13" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137381806</v>
       </c>
       <c r="B14" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137381699</v>
       </c>
       <c r="B15" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137381730</v>
       </c>
       <c r="B16" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137381739</v>
       </c>
       <c r="B17" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137381749</v>
       </c>
       <c r="B18" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137381877</v>
       </c>
       <c r="B19" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>137381682</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137381691</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137381694</v>
       </c>
       <c r="B23" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137381701</v>
       </c>
       <c r="B24" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137381709</v>
       </c>
       <c r="B25" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>137381689</v>
       </c>
       <c r="B26" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>137381768</v>
       </c>
       <c r="B27" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137381774</v>
       </c>
       <c r="B28" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>137381800</v>
       </c>
       <c r="B29" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137381723</v>
       </c>
       <c r="B30" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137381771</v>
       </c>
       <c r="B31" t="n">
-        <v>92851</v>
+        <v>92863</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137381692</v>
       </c>
       <c r="B32" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137381828</v>
       </c>
       <c r="B33" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137381841</v>
       </c>
       <c r="B34" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>137381887</v>
       </c>
       <c r="B35" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>137381690</v>
       </c>
       <c r="B36" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>137381802</v>
       </c>
       <c r="B37" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>137381807</v>
       </c>
       <c r="B38" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>137381829</v>
       </c>
       <c r="B39" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137381698</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137381700</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137381702</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>137381703</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>137381704</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>137381706</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>137381708</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137381711</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137381718</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137381720</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>137381721</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>137381724</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>137381729</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>137381734</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>137381735</v>
       </c>
       <c r="B55" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>137381736</v>
       </c>
       <c r="B56" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>137381738</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137381740</v>
       </c>
       <c r="B58" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>137381743</v>
       </c>
       <c r="B59" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>137381746</v>
       </c>
       <c r="B60" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137381747</v>
       </c>
       <c r="B61" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>137381750</v>
       </c>
       <c r="B62" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>137381752</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137381754</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>137381757</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>137381759</v>
       </c>
       <c r="B66" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>137381760</v>
       </c>
       <c r="B67" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137381761</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>137381764</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>137381765</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>137381772</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>137381773</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>137381775</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>137381776</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>137381779</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137381780</v>
       </c>
       <c r="B76" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137381783</v>
       </c>
       <c r="B77" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137381786</v>
       </c>
       <c r="B78" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137381789</v>
       </c>
       <c r="B79" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>137381790</v>
       </c>
       <c r="B80" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137381791</v>
       </c>
       <c r="B81" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137381793</v>
       </c>
       <c r="B82" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>137381797</v>
       </c>
       <c r="B83" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137381801</v>
       </c>
       <c r="B84" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>137381803</v>
       </c>
       <c r="B85" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>137381810</v>
       </c>
       <c r="B86" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>137381811</v>
       </c>
       <c r="B87" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137381812</v>
       </c>
       <c r="B88" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137381813</v>
       </c>
       <c r="B89" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137381814</v>
       </c>
       <c r="B90" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>137381815</v>
       </c>
       <c r="B91" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>137381816</v>
       </c>
       <c r="B92" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>137381817</v>
       </c>
       <c r="B93" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>137381819</v>
       </c>
       <c r="B94" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137381824</v>
       </c>
       <c r="B95" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>137381831</v>
       </c>
       <c r="B96" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>137381833</v>
       </c>
       <c r="B97" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>137381834</v>
       </c>
       <c r="B98" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137381835</v>
       </c>
       <c r="B99" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137381836</v>
       </c>
       <c r="B100" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137381843</v>
       </c>
       <c r="B101" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137381844</v>
       </c>
       <c r="B102" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>137381845</v>
       </c>
       <c r="B103" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137381847</v>
       </c>
       <c r="B104" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137381848</v>
       </c>
       <c r="B105" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>137381852</v>
       </c>
       <c r="B106" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>137381853</v>
       </c>
       <c r="B107" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>137381854</v>
       </c>
       <c r="B108" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>137381855</v>
       </c>
       <c r="B109" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137381859</v>
       </c>
       <c r="B110" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137381861</v>
       </c>
       <c r="B111" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137381863</v>
       </c>
       <c r="B112" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137381864</v>
       </c>
       <c r="B113" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>137381867</v>
       </c>
       <c r="B114" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>137381868</v>
       </c>
       <c r="B115" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>137381869</v>
       </c>
       <c r="B116" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>137381871</v>
       </c>
       <c r="B117" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>137381874</v>
       </c>
       <c r="B118" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>137381875</v>
       </c>
       <c r="B119" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>137381876</v>
       </c>
       <c r="B120" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>137381878</v>
       </c>
       <c r="B121" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>137381879</v>
       </c>
       <c r="B122" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137381688</v>
       </c>
       <c r="B123" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>137381732</v>
       </c>
       <c r="B124" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>137381733</v>
       </c>
       <c r="B125" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>137381753</v>
       </c>
       <c r="B126" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>137381858</v>
       </c>
       <c r="B127" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>137381686</v>
       </c>
       <c r="B128" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>137381839</v>
       </c>
       <c r="B129" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>137381707</v>
       </c>
       <c r="B130" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>137381808</v>
       </c>
       <c r="B131" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>137381717</v>
       </c>
       <c r="B132" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>137381683</v>
       </c>
       <c r="B162" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>137381685</v>
       </c>
       <c r="B163" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>137381697</v>
       </c>
       <c r="B164" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>137381713</v>
       </c>
       <c r="B165" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>137381818</v>
       </c>
       <c r="B166" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>137381695</v>
       </c>
       <c r="B167" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>137381821</v>
       </c>
       <c r="B168" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>137381823</v>
       </c>
       <c r="B169" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>137381693</v>
       </c>
       <c r="B171" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>137381716</v>
       </c>
       <c r="B172" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 41948-2026 artfynd.xlsx
+++ b/artfynd/A 41948-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137381767</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381755</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381784</v>
       </c>
       <c r="B4" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137381785</v>
       </c>
       <c r="B5" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137381787</v>
       </c>
       <c r="B6" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381842</v>
       </c>
       <c r="B7" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137381849</v>
       </c>
       <c r="B8" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137381862</v>
       </c>
       <c r="B9" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137381715</v>
       </c>
       <c r="B10" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137381782</v>
       </c>
       <c r="B11" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137381837</v>
       </c>
       <c r="B12" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137381769</v>
       </c>
       <c r="B13" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137381806</v>
       </c>
       <c r="B14" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137381699</v>
       </c>
       <c r="B15" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137381730</v>
       </c>
       <c r="B16" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137381739</v>
       </c>
       <c r="B17" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137381749</v>
       </c>
       <c r="B18" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137381877</v>
       </c>
       <c r="B19" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>137381682</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137381691</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137381694</v>
       </c>
       <c r="B23" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137381701</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137381709</v>
       </c>
       <c r="B25" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>137381689</v>
       </c>
       <c r="B26" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>137381768</v>
       </c>
       <c r="B27" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137381774</v>
       </c>
       <c r="B28" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>137381800</v>
       </c>
       <c r="B29" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137381723</v>
       </c>
       <c r="B30" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137381771</v>
       </c>
       <c r="B31" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137381692</v>
       </c>
       <c r="B32" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137381828</v>
       </c>
       <c r="B33" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137381841</v>
       </c>
       <c r="B34" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>137381887</v>
       </c>
       <c r="B35" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>137381690</v>
       </c>
       <c r="B36" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>137381802</v>
       </c>
       <c r="B37" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>137381807</v>
       </c>
       <c r="B38" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>137381829</v>
       </c>
       <c r="B39" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137381698</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137381700</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137381702</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>137381703</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>137381704</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>137381706</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>137381708</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137381711</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137381718</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137381720</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>137381721</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>137381724</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>137381729</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>137381734</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>137381735</v>
       </c>
       <c r="B55" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>137381736</v>
       </c>
       <c r="B56" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>137381738</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137381740</v>
       </c>
       <c r="B58" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>137381743</v>
       </c>
       <c r="B59" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>137381746</v>
       </c>
       <c r="B60" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137381747</v>
       </c>
       <c r="B61" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>137381750</v>
       </c>
       <c r="B62" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>137381752</v>
       </c>
       <c r="B63" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137381754</v>
       </c>
       <c r="B64" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>137381757</v>
       </c>
       <c r="B65" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>137381759</v>
       </c>
       <c r="B66" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>137381760</v>
       </c>
       <c r="B67" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137381761</v>
       </c>
       <c r="B68" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>137381764</v>
       </c>
       <c r="B69" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>137381765</v>
       </c>
       <c r="B70" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>137381772</v>
       </c>
       <c r="B71" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>137381773</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>137381775</v>
       </c>
       <c r="B73" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>137381776</v>
       </c>
       <c r="B74" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>137381779</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137381780</v>
       </c>
       <c r="B76" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137381783</v>
       </c>
       <c r="B77" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137381786</v>
       </c>
       <c r="B78" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137381789</v>
       </c>
       <c r="B79" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>137381790</v>
       </c>
       <c r="B80" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137381791</v>
       </c>
       <c r="B81" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137381793</v>
       </c>
       <c r="B82" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>137381797</v>
       </c>
       <c r="B83" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137381801</v>
       </c>
       <c r="B84" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>137381803</v>
       </c>
       <c r="B85" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>137381810</v>
       </c>
       <c r="B86" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>137381811</v>
       </c>
       <c r="B87" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137381812</v>
       </c>
       <c r="B88" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137381813</v>
       </c>
       <c r="B89" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137381814</v>
       </c>
       <c r="B90" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>137381815</v>
       </c>
       <c r="B91" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>137381816</v>
       </c>
       <c r="B92" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>137381817</v>
       </c>
       <c r="B93" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>137381819</v>
       </c>
       <c r="B94" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137381824</v>
       </c>
       <c r="B95" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>137381831</v>
       </c>
       <c r="B96" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>137381833</v>
       </c>
       <c r="B97" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>137381834</v>
       </c>
       <c r="B98" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137381835</v>
       </c>
       <c r="B99" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137381836</v>
       </c>
       <c r="B100" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137381843</v>
       </c>
       <c r="B101" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137381844</v>
       </c>
       <c r="B102" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>137381845</v>
       </c>
       <c r="B103" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137381847</v>
       </c>
       <c r="B104" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137381848</v>
       </c>
       <c r="B105" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>137381852</v>
       </c>
       <c r="B106" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>137381853</v>
       </c>
       <c r="B107" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>137381854</v>
       </c>
       <c r="B108" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>137381855</v>
       </c>
       <c r="B109" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137381859</v>
       </c>
       <c r="B110" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137381861</v>
       </c>
       <c r="B111" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137381863</v>
       </c>
       <c r="B112" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137381864</v>
       </c>
       <c r="B113" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>137381867</v>
       </c>
       <c r="B114" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>137381868</v>
       </c>
       <c r="B115" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>137381869</v>
       </c>
       <c r="B116" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>137381871</v>
       </c>
       <c r="B117" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>137381874</v>
       </c>
       <c r="B118" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>137381875</v>
       </c>
       <c r="B119" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>137381876</v>
       </c>
       <c r="B120" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>137381878</v>
       </c>
       <c r="B121" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>137381879</v>
       </c>
       <c r="B122" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137381688</v>
       </c>
       <c r="B123" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>137381732</v>
       </c>
       <c r="B124" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>137381733</v>
       </c>
       <c r="B125" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>137381753</v>
       </c>
       <c r="B126" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>137381858</v>
       </c>
       <c r="B127" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>137381686</v>
       </c>
       <c r="B128" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>137381839</v>
       </c>
       <c r="B129" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>137381707</v>
       </c>
       <c r="B130" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>137381808</v>
       </c>
       <c r="B131" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>137381717</v>
       </c>
       <c r="B132" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>137381683</v>
       </c>
       <c r="B162" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>137381685</v>
       </c>
       <c r="B163" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>137381697</v>
       </c>
       <c r="B164" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>137381713</v>
       </c>
       <c r="B165" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>137381818</v>
       </c>
       <c r="B166" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>137381695</v>
       </c>
       <c r="B167" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>137381821</v>
       </c>
       <c r="B168" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>137381823</v>
       </c>
       <c r="B169" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>137381693</v>
       </c>
       <c r="B171" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>137381716</v>
       </c>
       <c r="B172" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 41948-2026 artfynd.xlsx
+++ b/artfynd/A 41948-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137381767</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381755</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381784</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137381785</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137381787</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381842</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137381849</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137381862</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137381715</v>
       </c>
       <c r="B10" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137381782</v>
       </c>
       <c r="B11" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137381837</v>
       </c>
       <c r="B12" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137381769</v>
       </c>
       <c r="B13" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137381806</v>
       </c>
       <c r="B14" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137381699</v>
       </c>
       <c r="B15" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137381730</v>
       </c>
       <c r="B16" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137381739</v>
       </c>
       <c r="B17" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137381749</v>
       </c>
       <c r="B18" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137381877</v>
       </c>
       <c r="B19" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>137381682</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137381691</v>
       </c>
       <c r="B22" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137381694</v>
       </c>
       <c r="B23" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137381701</v>
       </c>
       <c r="B24" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137381709</v>
       </c>
       <c r="B25" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>137381689</v>
       </c>
       <c r="B26" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>137381768</v>
       </c>
       <c r="B27" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137381774</v>
       </c>
       <c r="B28" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>137381800</v>
       </c>
       <c r="B29" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137381723</v>
       </c>
       <c r="B30" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137381771</v>
       </c>
       <c r="B31" t="n">
-        <v>92864</v>
+        <v>92867</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137381692</v>
       </c>
       <c r="B32" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137381828</v>
       </c>
       <c r="B33" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137381841</v>
       </c>
       <c r="B34" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>137381887</v>
       </c>
       <c r="B35" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>137381690</v>
       </c>
       <c r="B36" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>137381802</v>
       </c>
       <c r="B37" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>137381807</v>
       </c>
       <c r="B38" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>137381829</v>
       </c>
       <c r="B39" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137381698</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137381700</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137381702</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>137381703</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>137381704</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>137381706</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>137381708</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137381711</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137381718</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137381720</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>137381721</v>
       </c>
       <c r="B51" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>137381724</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>137381729</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>137381734</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>137381735</v>
       </c>
       <c r="B55" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>137381736</v>
       </c>
       <c r="B56" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>137381738</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137381740</v>
       </c>
       <c r="B58" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>137381743</v>
       </c>
       <c r="B59" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>137381746</v>
       </c>
       <c r="B60" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137381747</v>
       </c>
       <c r="B61" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>137381750</v>
       </c>
       <c r="B62" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>137381752</v>
       </c>
       <c r="B63" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137381754</v>
       </c>
       <c r="B64" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>137381757</v>
       </c>
       <c r="B65" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>137381759</v>
       </c>
       <c r="B66" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>137381760</v>
       </c>
       <c r="B67" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137381761</v>
       </c>
       <c r="B68" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>137381764</v>
       </c>
       <c r="B69" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>137381765</v>
       </c>
       <c r="B70" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>137381772</v>
       </c>
       <c r="B71" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>137381773</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>137381775</v>
       </c>
       <c r="B73" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>137381776</v>
       </c>
       <c r="B74" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>137381779</v>
       </c>
       <c r="B75" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137381780</v>
       </c>
       <c r="B76" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137381783</v>
       </c>
       <c r="B77" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137381786</v>
       </c>
       <c r="B78" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137381789</v>
       </c>
       <c r="B79" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>137381790</v>
       </c>
       <c r="B80" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137381791</v>
       </c>
       <c r="B81" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137381793</v>
       </c>
       <c r="B82" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>137381797</v>
       </c>
       <c r="B83" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137381801</v>
       </c>
       <c r="B84" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>137381803</v>
       </c>
       <c r="B85" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>137381810</v>
       </c>
       <c r="B86" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>137381811</v>
       </c>
       <c r="B87" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137381812</v>
       </c>
       <c r="B88" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137381813</v>
       </c>
       <c r="B89" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137381814</v>
       </c>
       <c r="B90" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>137381815</v>
       </c>
       <c r="B91" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>137381816</v>
       </c>
       <c r="B92" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>137381817</v>
       </c>
       <c r="B93" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>137381819</v>
       </c>
       <c r="B94" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137381824</v>
       </c>
       <c r="B95" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>137381831</v>
       </c>
       <c r="B96" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>137381833</v>
       </c>
       <c r="B97" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>137381834</v>
       </c>
       <c r="B98" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137381835</v>
       </c>
       <c r="B99" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137381836</v>
       </c>
       <c r="B100" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137381843</v>
       </c>
       <c r="B101" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137381844</v>
       </c>
       <c r="B102" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>137381845</v>
       </c>
       <c r="B103" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137381847</v>
       </c>
       <c r="B104" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137381848</v>
       </c>
       <c r="B105" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>137381852</v>
       </c>
       <c r="B106" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>137381853</v>
       </c>
       <c r="B107" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>137381854</v>
       </c>
       <c r="B108" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>137381855</v>
       </c>
       <c r="B109" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137381859</v>
       </c>
       <c r="B110" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137381861</v>
       </c>
       <c r="B111" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137381863</v>
       </c>
       <c r="B112" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137381864</v>
       </c>
       <c r="B113" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>137381867</v>
       </c>
       <c r="B114" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>137381868</v>
       </c>
       <c r="B115" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>137381869</v>
       </c>
       <c r="B116" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>137381871</v>
       </c>
       <c r="B117" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>137381874</v>
       </c>
       <c r="B118" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>137381875</v>
       </c>
       <c r="B119" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>137381876</v>
       </c>
       <c r="B120" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>137381878</v>
       </c>
       <c r="B121" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>137381879</v>
       </c>
       <c r="B122" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137381688</v>
       </c>
       <c r="B123" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>137381732</v>
       </c>
       <c r="B124" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>137381733</v>
       </c>
       <c r="B125" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>137381753</v>
       </c>
       <c r="B126" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>137381858</v>
       </c>
       <c r="B127" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>137381686</v>
       </c>
       <c r="B128" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>137381839</v>
       </c>
       <c r="B129" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>137381707</v>
       </c>
       <c r="B130" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>137381808</v>
       </c>
       <c r="B131" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>137381717</v>
       </c>
       <c r="B132" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>137381683</v>
       </c>
       <c r="B162" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>137381685</v>
       </c>
       <c r="B163" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>137381697</v>
       </c>
       <c r="B164" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>137381713</v>
       </c>
       <c r="B165" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>137381818</v>
       </c>
       <c r="B166" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>137381695</v>
       </c>
       <c r="B167" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>137381821</v>
       </c>
       <c r="B168" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>137381823</v>
       </c>
       <c r="B169" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>137381693</v>
       </c>
       <c r="B171" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>137381716</v>
       </c>
       <c r="B172" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 41948-2026 artfynd.xlsx
+++ b/artfynd/A 41948-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137381767</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137381755</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137381784</v>
       </c>
       <c r="B4" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137381785</v>
       </c>
       <c r="B5" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137381787</v>
       </c>
       <c r="B6" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137381842</v>
       </c>
       <c r="B7" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137381849</v>
       </c>
       <c r="B8" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137381862</v>
       </c>
       <c r="B9" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137381715</v>
       </c>
       <c r="B10" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137381782</v>
       </c>
       <c r="B11" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137381837</v>
       </c>
       <c r="B12" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137381769</v>
       </c>
       <c r="B13" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137381806</v>
       </c>
       <c r="B14" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137381699</v>
       </c>
       <c r="B15" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137381730</v>
       </c>
       <c r="B16" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137381739</v>
       </c>
       <c r="B17" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137381749</v>
       </c>
       <c r="B18" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137381877</v>
       </c>
       <c r="B19" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>137381682</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137381691</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137381694</v>
       </c>
       <c r="B23" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>137381701</v>
       </c>
       <c r="B24" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>137381709</v>
       </c>
       <c r="B25" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>137381689</v>
       </c>
       <c r="B26" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>137381768</v>
       </c>
       <c r="B27" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>137381774</v>
       </c>
       <c r="B28" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>137381800</v>
       </c>
       <c r="B29" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>137381723</v>
       </c>
       <c r="B30" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>137381771</v>
       </c>
       <c r="B31" t="n">
-        <v>92867</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>137381692</v>
       </c>
       <c r="B32" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>137381828</v>
       </c>
       <c r="B33" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137381841</v>
       </c>
       <c r="B34" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>137381887</v>
       </c>
       <c r="B35" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>137381690</v>
       </c>
       <c r="B36" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>137381802</v>
       </c>
       <c r="B37" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>137381807</v>
       </c>
       <c r="B38" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>137381829</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137381698</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137381700</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137381702</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>137381703</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>137381704</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>137381706</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>137381708</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>137381711</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>137381718</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>137381720</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>137381721</v>
       </c>
       <c r="B51" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>137381724</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>137381729</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>137381734</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>137381735</v>
       </c>
       <c r="B55" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>137381736</v>
       </c>
       <c r="B56" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>137381738</v>
       </c>
       <c r="B57" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>137381740</v>
       </c>
       <c r="B58" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>137381743</v>
       </c>
       <c r="B59" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>137381746</v>
       </c>
       <c r="B60" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137381747</v>
       </c>
       <c r="B61" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>137381750</v>
       </c>
       <c r="B62" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>137381752</v>
       </c>
       <c r="B63" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>137381754</v>
       </c>
       <c r="B64" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>137381757</v>
       </c>
       <c r="B65" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>137381759</v>
       </c>
       <c r="B66" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>137381760</v>
       </c>
       <c r="B67" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>137381761</v>
       </c>
       <c r="B68" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>137381764</v>
       </c>
       <c r="B69" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>137381765</v>
       </c>
       <c r="B70" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>137381772</v>
       </c>
       <c r="B71" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>137381773</v>
       </c>
       <c r="B72" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>137381775</v>
       </c>
       <c r="B73" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>137381776</v>
       </c>
       <c r="B74" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>137381779</v>
       </c>
       <c r="B75" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>137381780</v>
       </c>
       <c r="B76" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>137381783</v>
       </c>
       <c r="B77" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>137381786</v>
       </c>
       <c r="B78" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>137381789</v>
       </c>
       <c r="B79" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>137381790</v>
       </c>
       <c r="B80" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137381791</v>
       </c>
       <c r="B81" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>137381793</v>
       </c>
       <c r="B82" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>137381797</v>
       </c>
       <c r="B83" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>137381801</v>
       </c>
       <c r="B84" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>137381803</v>
       </c>
       <c r="B85" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>137381810</v>
       </c>
       <c r="B86" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>137381811</v>
       </c>
       <c r="B87" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137381812</v>
       </c>
       <c r="B88" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>137381813</v>
       </c>
       <c r="B89" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137381814</v>
       </c>
       <c r="B90" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>137381815</v>
       </c>
       <c r="B91" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>137381816</v>
       </c>
       <c r="B92" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>137381817</v>
       </c>
       <c r="B93" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>137381819</v>
       </c>
       <c r="B94" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>137381824</v>
       </c>
       <c r="B95" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>137381831</v>
       </c>
       <c r="B96" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>137381833</v>
       </c>
       <c r="B97" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>137381834</v>
       </c>
       <c r="B98" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>137381835</v>
       </c>
       <c r="B99" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>137381836</v>
       </c>
       <c r="B100" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>137381843</v>
       </c>
       <c r="B101" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137381844</v>
       </c>
       <c r="B102" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>137381845</v>
       </c>
       <c r="B103" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>137381847</v>
       </c>
       <c r="B104" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>137381848</v>
       </c>
       <c r="B105" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>137381852</v>
       </c>
       <c r="B106" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>137381853</v>
       </c>
       <c r="B107" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>137381854</v>
       </c>
       <c r="B108" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>137381855</v>
       </c>
       <c r="B109" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>137381859</v>
       </c>
       <c r="B110" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>137381861</v>
       </c>
       <c r="B111" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>137381863</v>
       </c>
       <c r="B112" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>137381864</v>
       </c>
       <c r="B113" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>137381867</v>
       </c>
       <c r="B114" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>137381868</v>
       </c>
       <c r="B115" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>137381869</v>
       </c>
       <c r="B116" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>137381871</v>
       </c>
       <c r="B117" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>137381874</v>
       </c>
       <c r="B118" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>137381875</v>
       </c>
       <c r="B119" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>137381876</v>
       </c>
       <c r="B120" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>137381878</v>
       </c>
       <c r="B121" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>137381879</v>
       </c>
       <c r="B122" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>137381688</v>
       </c>
       <c r="B123" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>137381732</v>
       </c>
       <c r="B124" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>137381733</v>
       </c>
       <c r="B125" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>137381753</v>
       </c>
       <c r="B126" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>137381858</v>
       </c>
       <c r="B127" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>137381686</v>
       </c>
       <c r="B128" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>137381839</v>
       </c>
       <c r="B129" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>137381707</v>
       </c>
       <c r="B130" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>137381808</v>
       </c>
       <c r="B131" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>137381717</v>
       </c>
       <c r="B132" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>137381710</v>
       </c>
       <c r="B134" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>137381778</v>
       </c>
       <c r="B135" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>137381696</v>
       </c>
       <c r="B136" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>137381712</v>
       </c>
       <c r="B137" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>137381714</v>
       </c>
       <c r="B138" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>137381719</v>
       </c>
       <c r="B139" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>137381728</v>
       </c>
       <c r="B140" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>137381745</v>
       </c>
       <c r="B141" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>137381762</v>
       </c>
       <c r="B142" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>137381763</v>
       </c>
       <c r="B143" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>137381766</v>
       </c>
       <c r="B144" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>137381792</v>
       </c>
       <c r="B145" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>137381804</v>
       </c>
       <c r="B146" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>137381846</v>
       </c>
       <c r="B147" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>137381777</v>
       </c>
       <c r="B148" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>137381683</v>
       </c>
       <c r="B162" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>137381685</v>
       </c>
       <c r="B163" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>137381697</v>
       </c>
       <c r="B164" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>137381713</v>
       </c>
       <c r="B165" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>137381818</v>
       </c>
       <c r="B166" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>137381695</v>
       </c>
       <c r="B167" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>137381821</v>
       </c>
       <c r="B168" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>137381823</v>
       </c>
       <c r="B169" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>137381693</v>
       </c>
       <c r="B171" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>137381716</v>
       </c>
       <c r="B172" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
